--- a/publication_tables/supplementary/S17_equilibrium_feedback_decomposition.xlsx
+++ b/publication_tables/supplementary/S17_equilibrium_feedback_decomposition.xlsx
@@ -449,16 +449,16 @@
         <v>4.30572686665</v>
       </c>
       <c r="B2" t="n">
-        <v>6.67492490099</v>
+        <v>6.68138794627</v>
       </c>
       <c r="C2" t="n">
-        <v>6.66892752787</v>
+        <v>6.67504898442</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00599737311267</v>
+        <v>0.00633896184477</v>
       </c>
       <c r="E2" t="n">
-        <v>130.508030708</v>
+        <v>130.648894579</v>
       </c>
     </row>
     <row r="3">
@@ -466,16 +466,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>6.84704874018</v>
+        <v>6.85348083874</v>
       </c>
       <c r="C3" t="n">
-        <v>6.84112499857</v>
+        <v>6.84722942419</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0059237416086</v>
+        <v>0.00625141454923</v>
       </c>
       <c r="E3" t="n">
-        <v>130.550071136</v>
+        <v>130.688734874</v>
       </c>
     </row>
     <row r="4">
@@ -483,16 +483,16 @@
         <v>20</v>
       </c>
       <c r="B4" t="n">
-        <v>7.04707953583</v>
+        <v>7.0534291339</v>
       </c>
       <c r="C4" t="n">
-        <v>7.04150012557</v>
+        <v>7.04753308931</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00557941025864</v>
+        <v>0.00589604459342</v>
       </c>
       <c r="E4" t="n">
-        <v>130.576085809</v>
+        <v>130.711839056</v>
       </c>
     </row>
     <row r="5">
@@ -500,16 +500,16 @@
         <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>7.33760446197</v>
+        <v>7.34400418275</v>
       </c>
       <c r="C5" t="n">
-        <v>7.33259091747</v>
+        <v>7.33868459222</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00501354450609</v>
+        <v>0.00531959052707</v>
       </c>
       <c r="E5" t="n">
-        <v>130.590951494</v>
+        <v>130.72036103</v>
       </c>
     </row>
     <row r="6">
@@ -517,16 +517,16 @@
         <v>60</v>
       </c>
       <c r="B6" t="n">
-        <v>7.52170100872</v>
+        <v>7.52811171875</v>
       </c>
       <c r="C6" t="n">
-        <v>7.51704502455</v>
+        <v>7.52321787969</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00465598416903</v>
+        <v>0.00489383906159</v>
       </c>
       <c r="E6" t="n">
-        <v>130.566721183</v>
+        <v>130.690135039</v>
       </c>
     </row>
     <row r="7">
@@ -534,16 +534,16 @@
         <v>100</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72523275207</v>
+        <v>7.73165753865</v>
       </c>
       <c r="C7" t="n">
-        <v>7.72142895845</v>
+        <v>7.7276444077</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00380379361584</v>
+        <v>0.00401313095667</v>
       </c>
       <c r="E7" t="n">
-        <v>130.406560957</v>
+        <v>130.514003412</v>
       </c>
     </row>
   </sheetData>
